--- a/database/seeders/Categories.xlsx
+++ b/database/seeders/Categories.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Category</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>max</t>
+  </si>
+  <si>
+    <t>is_active</t>
   </si>
 </sst>
 </file>
@@ -490,14 +493,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" customWidth="1"/>
     <col min="2" max="2" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -510,8 +513,11 @@
       <c r="D1" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -524,8 +530,11 @@
       <c r="D2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -538,8 +547,11 @@
       <c r="D3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -552,8 +564,11 @@
       <c r="D4">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -566,8 +581,11 @@
       <c r="D5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -580,8 +598,11 @@
       <c r="D6">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>12</v>
       </c>
@@ -594,8 +615,11 @@
       <c r="D7">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -608,8 +632,11 @@
       <c r="D8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -622,8 +649,11 @@
       <c r="D9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
@@ -636,8 +666,11 @@
       <c r="D10">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -650,8 +683,11 @@
       <c r="D11">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
@@ -664,8 +700,11 @@
       <c r="D12">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
@@ -678,8 +717,11 @@
       <c r="D13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
@@ -692,8 +734,11 @@
       <c r="D14">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
@@ -706,8 +751,11 @@
       <c r="D15">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
@@ -720,8 +768,11 @@
       <c r="D16">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -734,8 +785,11 @@
       <c r="D17">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
@@ -748,8 +802,11 @@
       <c r="D18">
         <v>80</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -762,8 +819,11 @@
       <c r="D19">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
@@ -776,8 +836,11 @@
       <c r="D20">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
@@ -789,6 +852,9 @@
       </c>
       <c r="D21">
         <v>3</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
